--- a/حاسبة_تكلفة_الطباعة_ثلاثية_الأبعاد.xlsx
+++ b/حاسبة_تكلفة_الطباعة_ثلاثية_الأبعاد.xlsx
@@ -13,8 +13,13 @@
     <sheet name="الحاسبة" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="سجل المشاريع" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="لوحة التحكم" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="فاتورة" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="المخزون" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="إحصائيات العملاء" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'فاتورة'!$A$1:$E$15</definedName>
+  </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -28,7 +33,7 @@
     <numFmt numFmtId="167" formatCode="#,##0.0&quot; ساعة&quot;"/>
     <numFmt numFmtId="168" formatCode="#,##0.00&quot; كجم&quot;"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="26">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -150,6 +155,23 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="20"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00E8590C"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
       <sz val="24"/>
     </font>
     <font>
@@ -157,11 +179,6 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="14"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -234,21 +251,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -355,6 +372,33 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="168" fontId="19" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -912,7 +956,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:F20"/>
+  <dimension ref="A2:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -935,7 +979,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Creality Hi + CFS   |   الإصدار 1.0</t>
+          <t>Creality Hi + CFS   |   الإصدار 1.5</t>
         </is>
       </c>
     </row>
@@ -978,50 +1022,92 @@
     <row r="13" ht="26" customHeight="1">
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>📚 سجل المشاريع</t>
+          <t>📄 فاتورة</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>سجّل مشاريعك وتابعها</t>
+          <t>فاتورة جاهزة للطباعة PDF</t>
         </is>
       </c>
     </row>
     <row r="15" ht="26" customHeight="1">
       <c r="B15" s="3" t="inlineStr">
         <is>
+          <t>📦 المخزون</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>أرصدة الفيلامنت وتنبيهات النقص</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="26" customHeight="1">
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>👥 إحصائيات العملاء</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>ربح ومبيعات كل عميل</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="26" customHeight="1">
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>📚 سجل المشاريع</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>سجّل مشاريعك وتابعها</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="26" customHeight="1">
+      <c r="B21" s="3" t="inlineStr">
+        <is>
           <t>📊 لوحة التحكم</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>إحصائيات وأرباح ورسوم بيانية</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>استخدم التبويبات في الأسفل للتنقل بين الأوراق.  الخلايا الصفراء = إدخال يدوي، والباقي يُحسب تلقائيًا.</t>
         </is>
       </c>
     </row>
-    <row r="20"/>
+    <row r="25"/>
   </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D7:F7"/>
+  <mergeCells count="19">
     <mergeCell ref="D11:F11"/>
     <mergeCell ref="D13:F13"/>
-    <mergeCell ref="B15:C15"/>
     <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="B21:C21"/>
     <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A19:F20"/>
     <mergeCell ref="A5:F5"/>
-    <mergeCell ref="B9:C9"/>
     <mergeCell ref="D9:F9"/>
+    <mergeCell ref="A24:F25"/>
+    <mergeCell ref="B17:C17"/>
     <mergeCell ref="A2:F4"/>
     <mergeCell ref="D15:F15"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D21:F21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3594,4 +3680,853 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00E8590C"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="44" t="inlineStr">
+        <is>
+          <t>🖨️  متجر الطباعة ثلاثية الأبعاد</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="45" t="inlineStr">
+        <is>
+          <t>فاتورة ضريبية / عرض سعر</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="22" t="inlineStr">
+        <is>
+          <t>رقم الفاتورة</t>
+        </is>
+      </c>
+      <c r="C5" s="46">
+        <f>'الحاسبة'!B6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>التاريخ</t>
+        </is>
+      </c>
+      <c r="C6" s="46">
+        <f>'الحاسبة'!D6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>العميل</t>
+        </is>
+      </c>
+      <c r="C7" s="46">
+        <f>'الحاسبة'!D5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="39" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B9" s="39" t="inlineStr">
+        <is>
+          <t>المنتج</t>
+        </is>
+      </c>
+      <c r="C9" s="39" t="inlineStr">
+        <is>
+          <t>الكمية</t>
+        </is>
+      </c>
+      <c r="D9" s="39" t="inlineStr">
+        <is>
+          <t>سعر الوحدة (ر.س)</t>
+        </is>
+      </c>
+      <c r="E9" s="39" t="inlineStr">
+        <is>
+          <t>الإجمالي (ر.س)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" s="47">
+        <f>'الحاسبة'!B5</f>
+        <v/>
+      </c>
+      <c r="C10" s="47">
+        <f>'الحاسبة'!B7</f>
+        <v/>
+      </c>
+      <c r="D10" s="48">
+        <f>'الحاسبة'!D40</f>
+        <v/>
+      </c>
+      <c r="E10" s="48">
+        <f>C10*D10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="D12" s="49" t="inlineStr">
+        <is>
+          <t>الإجمالي:</t>
+        </is>
+      </c>
+      <c r="E12" s="50">
+        <f>E10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="51" t="inlineStr">
+        <is>
+          <t>شكرًا لتعاملكم معنا — تُطبع هذه الورقة PDF عبر: ملف ← تصدير ← PDF (أو بزر الماكرو).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="A1:E2"/>
+    <mergeCell ref="A3:E3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00E8590C"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>📦  إدارة مخزون الفيلامنت</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="39" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B2" s="39" t="inlineStr">
+        <is>
+          <t>الفيلامنت (النوع - الشركة - اللون)</t>
+        </is>
+      </c>
+      <c r="C2" s="39" t="inlineStr">
+        <is>
+          <t>الرصيد الحالي (جم)</t>
+        </is>
+      </c>
+      <c r="D2" s="39" t="inlineStr">
+        <is>
+          <t>حد إعادة الطلب (جم)</t>
+        </is>
+      </c>
+      <c r="E2" s="39" t="inlineStr">
+        <is>
+          <t>الحالة</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="16" t="inlineStr">
+        <is>
+          <t>Silk PLA - eSun - Copper</t>
+        </is>
+      </c>
+      <c r="C3" s="16" t="n">
+        <v>380</v>
+      </c>
+      <c r="D3" s="16" t="n">
+        <v>200</v>
+      </c>
+      <c r="E3" s="52">
+        <f>IF(B3="","",IF(C3&lt;=D3,"⚠️ اطلب","✔ متوفر"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>PLA - Creality - Black</t>
+        </is>
+      </c>
+      <c r="C4" s="16" t="n">
+        <v>950</v>
+      </c>
+      <c r="D4" s="16" t="n">
+        <v>300</v>
+      </c>
+      <c r="E4" s="52">
+        <f>IF(B4="","",IF(C4&lt;=D4,"⚠️ اطلب","✔ متوفر"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="16" t="inlineStr">
+        <is>
+          <t>PETG - Sunlu - White</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="n">
+        <v>120</v>
+      </c>
+      <c r="D5" s="16" t="n">
+        <v>300</v>
+      </c>
+      <c r="E5" s="52">
+        <f>IF(B5="","",IF(C5&lt;=D5,"⚠️ اطلب","✔ متوفر"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="16" t="n"/>
+      <c r="C6" s="16" t="n"/>
+      <c r="D6" s="16" t="n"/>
+      <c r="E6" s="52">
+        <f>IF(B6="","",IF(C6&lt;=D6,"⚠️ اطلب","✔ متوفر"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="16" t="n"/>
+      <c r="C7" s="16" t="n"/>
+      <c r="D7" s="16" t="n"/>
+      <c r="E7" s="52">
+        <f>IF(B7="","",IF(C7&lt;=D7,"⚠️ اطلب","✔ متوفر"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="16" t="n"/>
+      <c r="C8" s="16" t="n"/>
+      <c r="D8" s="16" t="n"/>
+      <c r="E8" s="52">
+        <f>IF(B8="","",IF(C8&lt;=D8,"⚠️ اطلب","✔ متوفر"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="16" t="n"/>
+      <c r="C9" s="16" t="n"/>
+      <c r="D9" s="16" t="n"/>
+      <c r="E9" s="52">
+        <f>IF(B9="","",IF(C9&lt;=D9,"⚠️ اطلب","✔ متوفر"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="16" t="n"/>
+      <c r="C10" s="16" t="n"/>
+      <c r="D10" s="16" t="n"/>
+      <c r="E10" s="52">
+        <f>IF(B10="","",IF(C10&lt;=D10,"⚠️ اطلب","✔ متوفر"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="16" t="n"/>
+      <c r="C11" s="16" t="n"/>
+      <c r="D11" s="16" t="n"/>
+      <c r="E11" s="52">
+        <f>IF(B11="","",IF(C11&lt;=D11,"⚠️ اطلب","✔ متوفر"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="16" t="n"/>
+      <c r="C12" s="16" t="n"/>
+      <c r="D12" s="16" t="n"/>
+      <c r="E12" s="52">
+        <f>IF(B12="","",IF(C12&lt;=D12,"⚠️ اطلب","✔ متوفر"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="16" t="n"/>
+      <c r="C13" s="16" t="n"/>
+      <c r="D13" s="16" t="n"/>
+      <c r="E13" s="52">
+        <f>IF(B13="","",IF(C13&lt;=D13,"⚠️ اطلب","✔ متوفر"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="16" t="n"/>
+      <c r="C14" s="16" t="n"/>
+      <c r="D14" s="16" t="n"/>
+      <c r="E14" s="52">
+        <f>IF(B14="","",IF(C14&lt;=D14,"⚠️ اطلب","✔ متوفر"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" s="16" t="n"/>
+      <c r="C15" s="16" t="n"/>
+      <c r="D15" s="16" t="n"/>
+      <c r="E15" s="52">
+        <f>IF(B15="","",IF(C15&lt;=D15,"⚠️ اطلب","✔ متوفر"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" s="16" t="n"/>
+      <c r="C16" s="16" t="n"/>
+      <c r="D16" s="16" t="n"/>
+      <c r="E16" s="52">
+        <f>IF(B16="","",IF(C16&lt;=D16,"⚠️ اطلب","✔ متوفر"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" s="16" t="n"/>
+      <c r="C17" s="16" t="n"/>
+      <c r="D17" s="16" t="n"/>
+      <c r="E17" s="52">
+        <f>IF(B17="","",IF(C17&lt;=D17,"⚠️ اطلب","✔ متوفر"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" s="16" t="n"/>
+      <c r="C18" s="16" t="n"/>
+      <c r="D18" s="16" t="n"/>
+      <c r="E18" s="52">
+        <f>IF(B18="","",IF(C18&lt;=D18,"⚠️ اطلب","✔ متوفر"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" s="16" t="n"/>
+      <c r="C19" s="16" t="n"/>
+      <c r="D19" s="16" t="n"/>
+      <c r="E19" s="52">
+        <f>IF(B19="","",IF(C19&lt;=D19,"⚠️ اطلب","✔ متوفر"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" s="16" t="n"/>
+      <c r="C20" s="16" t="n"/>
+      <c r="D20" s="16" t="n"/>
+      <c r="E20" s="52">
+        <f>IF(B20="","",IF(C20&lt;=D20,"⚠️ اطلب","✔ متوفر"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="15" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" s="16" t="n"/>
+      <c r="C21" s="16" t="n"/>
+      <c r="D21" s="16" t="n"/>
+      <c r="E21" s="52">
+        <f>IF(B21="","",IF(C21&lt;=D21,"⚠️ اطلب","✔ متوفر"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" s="16" t="n"/>
+      <c r="C22" s="16" t="n"/>
+      <c r="D22" s="16" t="n"/>
+      <c r="E22" s="52">
+        <f>IF(B22="","",IF(C22&lt;=D22,"⚠️ اطلب","✔ متوفر"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>تظهر «⚠️ اطلب» عندما ينزل الرصيد إلى حد إعادة الطلب أو أقل.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A24:E24"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="B3:B22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>='قاعدة الفيلامنت'!$I$3:$I$32</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00E8590C"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>👥  إحصائيات العملاء</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="39" t="inlineStr">
+        <is>
+          <t>العميل</t>
+        </is>
+      </c>
+      <c r="B2" s="39" t="inlineStr">
+        <is>
+          <t>عدد المشاريع</t>
+        </is>
+      </c>
+      <c r="C2" s="39" t="inlineStr">
+        <is>
+          <t>إجمالي المبيعات (ر.س)</t>
+        </is>
+      </c>
+      <c r="D2" s="39" t="inlineStr">
+        <is>
+          <t>إجمالي الأرباح (ر.س)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>عميل 1</t>
+        </is>
+      </c>
+      <c r="B3" s="52">
+        <f>IF(A3="","",COUNTIF('سجل المشاريع'!$C$3:$C$52,A3))</f>
+        <v/>
+      </c>
+      <c r="C3" s="26">
+        <f>IF(A3="","",SUMIF('سجل المشاريع'!$C$3:$C$52,A3,'سجل المشاريع'!$N$3:$N$52))</f>
+        <v/>
+      </c>
+      <c r="D3" s="26">
+        <f>IF(A3="","",SUMIF('سجل المشاريع'!$C$3:$C$52,A3,'سجل المشاريع'!$M$3:$M$52))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>عميل 2</t>
+        </is>
+      </c>
+      <c r="B4" s="52">
+        <f>IF(A4="","",COUNTIF('سجل المشاريع'!$C$3:$C$52,A4))</f>
+        <v/>
+      </c>
+      <c r="C4" s="26">
+        <f>IF(A4="","",SUMIF('سجل المشاريع'!$C$3:$C$52,A4,'سجل المشاريع'!$N$3:$N$52))</f>
+        <v/>
+      </c>
+      <c r="D4" s="26">
+        <f>IF(A4="","",SUMIF('سجل المشاريع'!$C$3:$C$52,A4,'سجل المشاريع'!$M$3:$M$52))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="n"/>
+      <c r="B5" s="52">
+        <f>IF(A5="","",COUNTIF('سجل المشاريع'!$C$3:$C$52,A5))</f>
+        <v/>
+      </c>
+      <c r="C5" s="26">
+        <f>IF(A5="","",SUMIF('سجل المشاريع'!$C$3:$C$52,A5,'سجل المشاريع'!$N$3:$N$52))</f>
+        <v/>
+      </c>
+      <c r="D5" s="26">
+        <f>IF(A5="","",SUMIF('سجل المشاريع'!$C$3:$C$52,A5,'سجل المشاريع'!$M$3:$M$52))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="16" t="n"/>
+      <c r="B6" s="52">
+        <f>IF(A6="","",COUNTIF('سجل المشاريع'!$C$3:$C$52,A6))</f>
+        <v/>
+      </c>
+      <c r="C6" s="26">
+        <f>IF(A6="","",SUMIF('سجل المشاريع'!$C$3:$C$52,A6,'سجل المشاريع'!$N$3:$N$52))</f>
+        <v/>
+      </c>
+      <c r="D6" s="26">
+        <f>IF(A6="","",SUMIF('سجل المشاريع'!$C$3:$C$52,A6,'سجل المشاريع'!$M$3:$M$52))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="16" t="n"/>
+      <c r="B7" s="52">
+        <f>IF(A7="","",COUNTIF('سجل المشاريع'!$C$3:$C$52,A7))</f>
+        <v/>
+      </c>
+      <c r="C7" s="26">
+        <f>IF(A7="","",SUMIF('سجل المشاريع'!$C$3:$C$52,A7,'سجل المشاريع'!$N$3:$N$52))</f>
+        <v/>
+      </c>
+      <c r="D7" s="26">
+        <f>IF(A7="","",SUMIF('سجل المشاريع'!$C$3:$C$52,A7,'سجل المشاريع'!$M$3:$M$52))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="16" t="n"/>
+      <c r="B8" s="52">
+        <f>IF(A8="","",COUNTIF('سجل المشاريع'!$C$3:$C$52,A8))</f>
+        <v/>
+      </c>
+      <c r="C8" s="26">
+        <f>IF(A8="","",SUMIF('سجل المشاريع'!$C$3:$C$52,A8,'سجل المشاريع'!$N$3:$N$52))</f>
+        <v/>
+      </c>
+      <c r="D8" s="26">
+        <f>IF(A8="","",SUMIF('سجل المشاريع'!$C$3:$C$52,A8,'سجل المشاريع'!$M$3:$M$52))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="16" t="n"/>
+      <c r="B9" s="52">
+        <f>IF(A9="","",COUNTIF('سجل المشاريع'!$C$3:$C$52,A9))</f>
+        <v/>
+      </c>
+      <c r="C9" s="26">
+        <f>IF(A9="","",SUMIF('سجل المشاريع'!$C$3:$C$52,A9,'سجل المشاريع'!$N$3:$N$52))</f>
+        <v/>
+      </c>
+      <c r="D9" s="26">
+        <f>IF(A9="","",SUMIF('سجل المشاريع'!$C$3:$C$52,A9,'سجل المشاريع'!$M$3:$M$52))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="16" t="n"/>
+      <c r="B10" s="52">
+        <f>IF(A10="","",COUNTIF('سجل المشاريع'!$C$3:$C$52,A10))</f>
+        <v/>
+      </c>
+      <c r="C10" s="26">
+        <f>IF(A10="","",SUMIF('سجل المشاريع'!$C$3:$C$52,A10,'سجل المشاريع'!$N$3:$N$52))</f>
+        <v/>
+      </c>
+      <c r="D10" s="26">
+        <f>IF(A10="","",SUMIF('سجل المشاريع'!$C$3:$C$52,A10,'سجل المشاريع'!$M$3:$M$52))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="16" t="n"/>
+      <c r="B11" s="52">
+        <f>IF(A11="","",COUNTIF('سجل المشاريع'!$C$3:$C$52,A11))</f>
+        <v/>
+      </c>
+      <c r="C11" s="26">
+        <f>IF(A11="","",SUMIF('سجل المشاريع'!$C$3:$C$52,A11,'سجل المشاريع'!$N$3:$N$52))</f>
+        <v/>
+      </c>
+      <c r="D11" s="26">
+        <f>IF(A11="","",SUMIF('سجل المشاريع'!$C$3:$C$52,A11,'سجل المشاريع'!$M$3:$M$52))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="16" t="n"/>
+      <c r="B12" s="52">
+        <f>IF(A12="","",COUNTIF('سجل المشاريع'!$C$3:$C$52,A12))</f>
+        <v/>
+      </c>
+      <c r="C12" s="26">
+        <f>IF(A12="","",SUMIF('سجل المشاريع'!$C$3:$C$52,A12,'سجل المشاريع'!$N$3:$N$52))</f>
+        <v/>
+      </c>
+      <c r="D12" s="26">
+        <f>IF(A12="","",SUMIF('سجل المشاريع'!$C$3:$C$52,A12,'سجل المشاريع'!$M$3:$M$52))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="16" t="n"/>
+      <c r="B13" s="52">
+        <f>IF(A13="","",COUNTIF('سجل المشاريع'!$C$3:$C$52,A13))</f>
+        <v/>
+      </c>
+      <c r="C13" s="26">
+        <f>IF(A13="","",SUMIF('سجل المشاريع'!$C$3:$C$52,A13,'سجل المشاريع'!$N$3:$N$52))</f>
+        <v/>
+      </c>
+      <c r="D13" s="26">
+        <f>IF(A13="","",SUMIF('سجل المشاريع'!$C$3:$C$52,A13,'سجل المشاريع'!$M$3:$M$52))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="16" t="n"/>
+      <c r="B14" s="52">
+        <f>IF(A14="","",COUNTIF('سجل المشاريع'!$C$3:$C$52,A14))</f>
+        <v/>
+      </c>
+      <c r="C14" s="26">
+        <f>IF(A14="","",SUMIF('سجل المشاريع'!$C$3:$C$52,A14,'سجل المشاريع'!$N$3:$N$52))</f>
+        <v/>
+      </c>
+      <c r="D14" s="26">
+        <f>IF(A14="","",SUMIF('سجل المشاريع'!$C$3:$C$52,A14,'سجل المشاريع'!$M$3:$M$52))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="16" t="n"/>
+      <c r="B15" s="52">
+        <f>IF(A15="","",COUNTIF('سجل المشاريع'!$C$3:$C$52,A15))</f>
+        <v/>
+      </c>
+      <c r="C15" s="26">
+        <f>IF(A15="","",SUMIF('سجل المشاريع'!$C$3:$C$52,A15,'سجل المشاريع'!$N$3:$N$52))</f>
+        <v/>
+      </c>
+      <c r="D15" s="26">
+        <f>IF(A15="","",SUMIF('سجل المشاريع'!$C$3:$C$52,A15,'سجل المشاريع'!$M$3:$M$52))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="16" t="n"/>
+      <c r="B16" s="52">
+        <f>IF(A16="","",COUNTIF('سجل المشاريع'!$C$3:$C$52,A16))</f>
+        <v/>
+      </c>
+      <c r="C16" s="26">
+        <f>IF(A16="","",SUMIF('سجل المشاريع'!$C$3:$C$52,A16,'سجل المشاريع'!$N$3:$N$52))</f>
+        <v/>
+      </c>
+      <c r="D16" s="26">
+        <f>IF(A16="","",SUMIF('سجل المشاريع'!$C$3:$C$52,A16,'سجل المشاريع'!$M$3:$M$52))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="16" t="n"/>
+      <c r="B17" s="52">
+        <f>IF(A17="","",COUNTIF('سجل المشاريع'!$C$3:$C$52,A17))</f>
+        <v/>
+      </c>
+      <c r="C17" s="26">
+        <f>IF(A17="","",SUMIF('سجل المشاريع'!$C$3:$C$52,A17,'سجل المشاريع'!$N$3:$N$52))</f>
+        <v/>
+      </c>
+      <c r="D17" s="26">
+        <f>IF(A17="","",SUMIF('سجل المشاريع'!$C$3:$C$52,A17,'سجل المشاريع'!$M$3:$M$52))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="16" t="n"/>
+      <c r="B18" s="52">
+        <f>IF(A18="","",COUNTIF('سجل المشاريع'!$C$3:$C$52,A18))</f>
+        <v/>
+      </c>
+      <c r="C18" s="26">
+        <f>IF(A18="","",SUMIF('سجل المشاريع'!$C$3:$C$52,A18,'سجل المشاريع'!$N$3:$N$52))</f>
+        <v/>
+      </c>
+      <c r="D18" s="26">
+        <f>IF(A18="","",SUMIF('سجل المشاريع'!$C$3:$C$52,A18,'سجل المشاريع'!$M$3:$M$52))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="16" t="n"/>
+      <c r="B19" s="52">
+        <f>IF(A19="","",COUNTIF('سجل المشاريع'!$C$3:$C$52,A19))</f>
+        <v/>
+      </c>
+      <c r="C19" s="26">
+        <f>IF(A19="","",SUMIF('سجل المشاريع'!$C$3:$C$52,A19,'سجل المشاريع'!$N$3:$N$52))</f>
+        <v/>
+      </c>
+      <c r="D19" s="26">
+        <f>IF(A19="","",SUMIF('سجل المشاريع'!$C$3:$C$52,A19,'سجل المشاريع'!$M$3:$M$52))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="16" t="n"/>
+      <c r="B20" s="52">
+        <f>IF(A20="","",COUNTIF('سجل المشاريع'!$C$3:$C$52,A20))</f>
+        <v/>
+      </c>
+      <c r="C20" s="26">
+        <f>IF(A20="","",SUMIF('سجل المشاريع'!$C$3:$C$52,A20,'سجل المشاريع'!$N$3:$N$52))</f>
+        <v/>
+      </c>
+      <c r="D20" s="26">
+        <f>IF(A20="","",SUMIF('سجل المشاريع'!$C$3:$C$52,A20,'سجل المشاريع'!$M$3:$M$52))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="16" t="n"/>
+      <c r="B21" s="52">
+        <f>IF(A21="","",COUNTIF('سجل المشاريع'!$C$3:$C$52,A21))</f>
+        <v/>
+      </c>
+      <c r="C21" s="26">
+        <f>IF(A21="","",SUMIF('سجل المشاريع'!$C$3:$C$52,A21,'سجل المشاريع'!$N$3:$N$52))</f>
+        <v/>
+      </c>
+      <c r="D21" s="26">
+        <f>IF(A21="","",SUMIF('سجل المشاريع'!$C$3:$C$52,A21,'سجل المشاريع'!$M$3:$M$52))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="16" t="n"/>
+      <c r="B22" s="52">
+        <f>IF(A22="","",COUNTIF('سجل المشاريع'!$C$3:$C$52,A22))</f>
+        <v/>
+      </c>
+      <c r="C22" s="26">
+        <f>IF(A22="","",SUMIF('سجل المشاريع'!$C$3:$C$52,A22,'سجل المشاريع'!$N$3:$N$52))</f>
+        <v/>
+      </c>
+      <c r="D22" s="26">
+        <f>IF(A22="","",SUMIF('سجل المشاريع'!$C$3:$C$52,A22,'سجل المشاريع'!$M$3:$M$52))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>اكتب اسم العميل (كما في السجل) لتظهر إحصائياته تلقائيًا.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A24:D24"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>